--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,102 +531,214 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785494939</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>54.960725</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,102 +643,214 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,92 +531,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22.74</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.4138</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19603365</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>45.969789</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,102 +747,550 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,89 +635,81 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>19.02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.4138</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19603365</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>1785534359</t>
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +754,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>45.969789</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +866,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>3.80999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785533370</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>6.047603</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785531926</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>13.555556</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1090,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785494939</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>54.960725</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,102 +1187,214 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,31 +755,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -866,22 +866,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,39 +1075,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,12 +1194,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1217,7 +1209,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1227,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1346,55 +1338,5591 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785577149</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5.597908</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16.18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785577133</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>70.347826</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>29.98</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.2288</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785577133</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>131.060109</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>50.98871</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.4638</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785577133</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>109.948701</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>68.58259</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785577133</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>149.092587</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785577004</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10.869565</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785576974</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>21.73913</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>56.57148</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785576966</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>122.981478</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785576397</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3.914373</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785575922</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>9.247706</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>65.05999</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.7725</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785575922</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>84.220052</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.3188</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785575403</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>223.686275</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.3188</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785575290</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>6.682353</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10.45999</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.7725</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785575084</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13.54044</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4.99999</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.5463</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785574733</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>9.1533</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2.59139</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785574712</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>4.733132</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785574712</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>36.043478</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22.76</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.5425</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785574711</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>41.953917</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>65.38999</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.5387</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785574671</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>121.373531</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>18.41</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.235</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785574668</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>78.340426</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>110.32</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785574667</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>370.823529</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1e-05</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.235</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785574667</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>0.000043</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>39.62258</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.595</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785574666</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>66.592571</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>23.09033</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.4612</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785574666</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>50.060336</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8.39352</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2975</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785574666</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>28.213513</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22.83872</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.5437</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785574666</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>42.002244</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>99.66667</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785574665</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>216.666674</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9.83</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.2312</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785572695</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>42.508108</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>60.49999</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.7775</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785569861</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>77.813492</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20.57</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.2338</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785568816</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.3113</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Djurgardens IF</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>VasterAs SK FK</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19619060</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785567910</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785776400</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16.064257</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>15.85</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.3113</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Djurgardens IF</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>VasterAs SK FK</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19619060</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785567898</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785776400</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>50.923695</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.2263</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785566254</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>75.138122</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>10.89998</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.555</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785565064</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19.639604</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.99999</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.6713</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AIK vs Orgryte IS</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Orgryte IS</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19612553</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785564110</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785681000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1.489743</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>65.90999</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.7837</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785562879</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>84.095681</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>11.20999</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785561095</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>18.722322</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>27.47</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.5987</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785554384</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>45.878914</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.2125</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785554384</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>11.105882</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.45998</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.7837</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785551845</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>3.13873</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.4025</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785549936</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>45.118012</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>75.88</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.5587</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785542520</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>135.803132</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9.76138</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785542512</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>23.241381</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785542511</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>9.353846</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.1687</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785535711</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>17.718519</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>11.941176</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +643,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +739,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,31 +859,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -891,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,22 +970,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1003,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1107,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,39 +1171,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1219,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1275,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1323,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,27 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1423,34 +1403,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1483,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,47 +1498,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1630,12 +1606,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1696,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,31 +1699,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1770,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1800,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,31 +1811,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1874,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,23 +1923,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2008,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,23 +2027,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2059,7 +2055,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,39 +2139,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2194,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,12 +2243,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2266,22 +2258,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2306,7 +2298,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2338,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,23 +2355,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2387,7 +2383,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,39 +2467,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2522,7 +2514,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2552,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,39 +2571,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2634,7 +2618,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2664,7 +2648,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2658,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,23 +2675,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2738,7 +2722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,27 +2779,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2823,26 +2803,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -2880,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2890,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2907,7 +2883,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2915,19 +2891,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2935,26 +2907,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -2992,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3002,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3019,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3027,23 +2995,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3066,7 +3042,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3096,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3106,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,12 +3099,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3138,39 +3114,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -3178,7 +3154,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,27 +3211,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3263,26 +3235,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -3290,7 +3258,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3320,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3330,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3347,7 +3315,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3362,22 +3330,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3402,7 +3370,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3432,7 +3400,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3442,7 +3410,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3459,7 +3427,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3467,28 +3435,36 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -3506,7 +3482,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3536,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3546,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,7 +3539,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3571,19 +3547,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3591,11 +3563,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3648,7 +3616,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3658,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3675,31 +3643,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3722,7 +3698,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3752,7 +3728,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3762,7 +3738,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,31 +3755,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3826,7 +3810,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3856,7 +3840,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3866,7 +3850,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,28 +3867,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3930,7 +3914,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3960,7 +3944,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3970,7 +3954,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3987,12 +3971,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4002,12 +3986,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4072,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4082,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,7 +4083,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4107,15 +4091,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4123,7 +4111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4176,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4218,12 +4210,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4288,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4298,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,7 +4307,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4326,17 +4318,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4362,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,12 +4411,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4434,12 +4426,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4504,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4514,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,39 +4523,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4571,27 +4555,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4616,17 +4600,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4643,39 +4627,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4683,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4728,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4755,62 +4731,54 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4840,7 +4808,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4850,7 +4818,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4867,12 +4835,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4882,12 +4850,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4952,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4962,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4979,27 +4947,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5007,11 +4971,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5019,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5064,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5091,7 +5051,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5099,15 +5059,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5115,7 +5079,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5138,7 +5106,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5168,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5178,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5195,7 +5163,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5206,17 +5174,17 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5242,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5272,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5282,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5299,31 +5267,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5346,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5376,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5386,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5403,31 +5379,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5435,27 +5419,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5480,17 +5464,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5507,31 +5491,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5539,27 +5531,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5584,17 +5576,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,12 +5603,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5626,22 +5618,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IFK Göteborg -1</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5651,27 +5643,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5696,17 +5688,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5723,12 +5715,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5738,12 +5730,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5808,7 +5800,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5818,7 +5810,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5835,12 +5827,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5850,22 +5842,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5875,27 +5867,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5920,17 +5912,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5947,7 +5939,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5955,31 +5947,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6002,7 +5986,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6032,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6042,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6059,7 +6043,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6070,17 +6054,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6106,7 +6090,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6136,7 +6120,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6146,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6163,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6174,17 +6158,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6210,7 +6194,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6240,7 +6224,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6250,7 +6234,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6267,39 +6251,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6322,7 +6298,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6352,7 +6328,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6362,7 +6338,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6379,7 +6355,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6387,31 +6363,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6434,7 +6402,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6464,7 +6432,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6474,7 +6442,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6491,12 +6459,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6506,22 +6474,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6531,27 +6499,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6576,17 +6544,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6603,7 +6571,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6618,22 +6586,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6658,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6688,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6698,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6715,12 +6683,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6730,22 +6698,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6755,27 +6723,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6800,17 +6768,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6827,102 +6795,982 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785542511</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>9.353846</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.1687</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785535711</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>17.718519</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>11.941176</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +843,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,17 +854,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,67 +947,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1114,7 +1098,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1179,23 +1163,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1203,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,17 +1278,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1307,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,31 +1371,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1411,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,27 +1483,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1511,11 +1507,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1627,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,7 +1691,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1707,31 +1699,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1739,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1795,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1866,7 +1842,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1872,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1882,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,31 +1899,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1970,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,27 +2011,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2055,34 +2035,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2088,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2098,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,31 +2115,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2186,7 +2170,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,12 +2227,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2258,47 +2242,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2328,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,27 +2339,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2383,34 +2363,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,23 +2443,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2491,7 +2471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2514,7 +2498,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2544,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,23 +2555,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2648,7 +2632,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2658,7 +2642,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,23 +2659,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2699,7 +2687,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2722,7 +2714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2752,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,23 +2771,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2803,7 +2799,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2894,12 +2894,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,39 +2987,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3042,7 +3034,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3072,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3082,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,39 +3091,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3154,7 +3138,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3168,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3178,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3222,12 +3206,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3258,7 +3242,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,39 +3299,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3370,7 +3346,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3400,7 +3376,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3410,7 +3386,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,7 +3403,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3442,22 +3418,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3482,7 +3458,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3512,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,7 +3515,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3547,23 +3523,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3586,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,27 +3627,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3671,26 +3651,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -3698,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3728,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,12 +3731,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3770,39 +3746,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -3810,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3840,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,7 +3843,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3875,23 +3851,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3914,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3944,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3954,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,27 +3955,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3999,26 +3979,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4026,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4056,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,12 +4059,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4098,12 +4074,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4168,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4178,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,12 +4171,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4210,12 +4186,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4225,7 +4201,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4250,7 +4226,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4280,7 +4256,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4266,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,7 +4283,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4318,17 +4294,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4354,7 +4330,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4384,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4394,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,12 +4387,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4426,12 +4402,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4441,7 +4417,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4466,7 +4442,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4496,7 +4472,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4482,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,7 +4499,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4531,23 +4507,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4570,7 +4554,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4600,7 +4584,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4610,7 +4594,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,7 +4611,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4635,23 +4619,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4674,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4704,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,18 +4723,18 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4778,7 +4770,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4808,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,12 +4827,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4850,12 +4842,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4865,24 +4857,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4890,7 +4882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4939,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4958,17 +4950,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4994,7 +4986,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5016,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5026,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,7 +5043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5059,31 +5051,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5106,7 +5090,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5136,7 +5120,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5130,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,28 +5147,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5210,7 +5194,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5224,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5234,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,12 +5251,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5282,12 +5266,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5297,7 +5281,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5322,7 +5306,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5352,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5346,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,39 +5363,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5419,27 +5395,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5464,17 +5440,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,12 +5467,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5506,22 +5482,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5531,27 +5507,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5576,17 +5552,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,27 +5579,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5631,34 +5603,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5688,7 +5656,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5698,7 +5666,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5715,12 +5683,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5730,12 +5698,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5745,24 +5713,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5770,7 +5738,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5800,7 +5768,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5810,7 +5778,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5827,12 +5795,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5842,22 +5810,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5867,27 +5835,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5912,17 +5880,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5939,31 +5907,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5971,27 +5947,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6016,17 +5992,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,31 +6019,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6090,7 +6074,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6120,7 +6104,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6130,7 +6114,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,31 +6131,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6194,7 +6186,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6224,7 +6216,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6234,7 +6226,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6251,31 +6243,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6355,7 +6355,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6366,7 +6366,7 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6459,39 +6459,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6499,27 +6491,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6544,17 +6536,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,54 +6563,46 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -6626,7 +6610,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6656,7 +6640,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6666,7 +6650,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6683,7 +6667,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6691,31 +6675,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6738,7 +6714,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6768,7 +6744,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6778,7 +6754,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6795,7 +6771,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6803,31 +6779,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6850,7 +6818,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6880,7 +6848,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6890,7 +6858,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6907,31 +6875,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6939,27 +6915,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6984,17 +6960,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7011,31 +6987,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7058,7 +7042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7088,7 +7072,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7098,7 +7082,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7115,12 +7099,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7130,12 +7114,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7200,7 +7184,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7210,7 +7194,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7227,7 +7211,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7242,22 +7226,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7282,7 +7266,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7312,7 +7296,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7322,7 +7306,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7339,7 +7323,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7347,31 +7331,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7394,7 +7370,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7424,7 +7400,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7434,7 +7410,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,39 +7427,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7506,7 +7474,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7536,7 +7504,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7546,7 +7514,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7563,12 +7531,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7578,22 +7546,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7603,27 +7571,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7648,17 +7616,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>45.969789</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7675,102 +7643,550 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr">
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="T72" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="U72" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="V72" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,31 +755,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -771,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -851,15 +875,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -867,7 +895,11 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -875,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +979,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1098,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1128,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1170,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AIK -2</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1210,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,31 +1307,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1314,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1379,59 +1427,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,28 +1523,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1515,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1560,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,28 +1627,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1619,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1664,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1674,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1702,17 +1742,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1723,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1768,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,28 +1835,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1827,27 +1867,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1872,17 +1912,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1907,31 +1947,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1939,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,31 +2043,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2043,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2123,31 +2163,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2155,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2200,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2242,22 +2274,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2267,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2312,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,28 +2371,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2371,27 +2403,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2448,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,39 +2475,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2483,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,28 +2579,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2587,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2632,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,27 +2683,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2687,34 +2707,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,12 +2787,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2786,47 +2802,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2856,7 +2872,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2882,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2894,12 +2910,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2960,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,31 +3003,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3034,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3064,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3074,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,31 +3115,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3138,7 +3170,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,23 +3227,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3272,7 +3304,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,23 +3331,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3323,7 +3359,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3346,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3376,7 +3416,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3386,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,39 +3443,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3458,7 +3490,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3488,7 +3520,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3498,7 +3530,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,12 +3547,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3530,22 +3562,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3570,7 +3602,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3600,7 +3632,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3610,7 +3642,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,23 +3659,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3651,7 +3687,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3674,7 +3714,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3704,7 +3744,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3714,7 +3754,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,39 +3771,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3786,7 +3818,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3816,7 +3848,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3826,7 +3858,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,39 +3875,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3898,7 +3922,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3952,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,23 +3979,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4002,7 +4026,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4032,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,27 +4083,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4087,26 +4107,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4144,7 +4160,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4170,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4187,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4179,19 +4195,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4199,26 +4211,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4256,7 +4264,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4266,7 +4274,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4283,7 +4291,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4291,23 +4299,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4330,7 +4346,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4360,7 +4376,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4386,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,12 +4403,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4402,39 +4418,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4442,7 +4458,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4472,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4482,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4499,27 +4515,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4527,26 +4539,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -4554,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4584,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4626,22 +4634,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4666,7 +4674,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4704,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4714,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4731,28 +4739,36 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -4770,7 +4786,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4800,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4835,19 +4851,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4855,11 +4867,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,31 +4947,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4986,7 +5002,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5016,7 +5032,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5026,7 +5042,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5043,31 +5059,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5090,7 +5114,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5120,7 +5144,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5130,7 +5154,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5147,28 +5171,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5194,7 +5218,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5224,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5234,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5251,12 +5275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5266,12 +5290,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5336,7 +5360,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5346,7 +5370,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,7 +5387,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5371,15 +5395,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5387,7 +5415,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5440,7 +5472,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5450,7 +5482,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5467,7 +5499,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5482,12 +5514,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5552,7 +5584,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5562,7 +5594,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5579,7 +5611,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5590,17 +5622,17 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5626,7 +5658,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5656,7 +5688,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5666,7 +5698,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5683,12 +5715,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5698,12 +5730,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5768,7 +5800,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5778,7 +5810,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5795,39 +5827,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5835,27 +5859,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5880,17 +5904,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5907,39 +5931,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5947,27 +5963,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5992,17 +6008,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6019,62 +6035,54 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6104,7 +6112,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6114,7 +6122,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6131,12 +6139,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6146,12 +6154,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6216,7 +6224,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6226,7 +6234,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6243,27 +6251,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6271,11 +6275,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6355,7 +6355,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6363,15 +6363,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6379,7 +6383,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6402,7 +6410,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6432,7 +6440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6442,7 +6450,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6459,7 +6467,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6470,17 +6478,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6506,7 +6514,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6536,7 +6544,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6546,7 +6554,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6563,31 +6571,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6610,7 +6626,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6640,7 +6656,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6650,7 +6666,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,31 +6683,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6699,27 +6723,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6744,17 +6768,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6771,31 +6795,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6803,27 +6835,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6848,17 +6880,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6875,12 +6907,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6890,22 +6922,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>IFK Göteborg -1</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6915,27 +6947,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6960,17 +6992,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6987,12 +7019,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7002,12 +7034,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7072,7 +7104,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7082,7 +7114,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7099,12 +7131,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7114,22 +7146,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7139,27 +7171,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7184,17 +7216,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7211,7 +7243,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7219,31 +7251,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7266,7 +7290,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7296,7 +7320,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7306,7 +7330,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7323,7 +7347,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7334,17 +7358,17 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7370,7 +7394,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7400,7 +7424,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7410,7 +7434,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7427,7 +7451,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7438,17 +7462,17 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7474,7 +7498,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7504,7 +7528,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7514,7 +7538,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,39 +7555,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7586,7 +7602,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7616,7 +7632,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7626,7 +7642,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,7 +7659,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7651,31 +7667,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7698,7 +7706,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7728,7 +7736,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7738,7 +7746,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7755,12 +7763,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7770,22 +7778,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7795,27 +7803,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7840,17 +7848,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7867,7 +7875,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7882,22 +7890,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7922,7 +7930,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7952,7 +7960,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7962,7 +7970,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7979,12 +7987,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7994,22 +8002,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8019,27 +8027,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8064,17 +8072,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8091,102 +8099,982 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785542511</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>9.353846</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.1687</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785535711</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>17.718519</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>11.941176</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T80" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="U80" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="V80" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>IFK Göteborg -0.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -810,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,39 +851,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -907,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -987,23 +963,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1011,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1082,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1194,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1250,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1280,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1290,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1291,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1306,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1362,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1392,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1402,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1427,23 +1411,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1451,27 +1443,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1488,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,28 +1515,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1570,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,31 +1619,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1659,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1763,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1867,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,28 +1955,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1971,27 +1987,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2016,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2083,27 +2091,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2128,17 +2136,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,28 +2163,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2187,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,59 +2275,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,28 +2371,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,28 +2475,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2587,23 +2587,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2611,27 +2619,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2664,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,23 +2691,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2715,27 +2723,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2768,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,22 +2810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2827,27 +2835,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2880,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,28 +2907,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2931,27 +2939,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2976,17 +2984,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,7 +3011,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3011,31 +3019,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3043,27 +3043,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,7 +3115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3123,31 +3123,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3155,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3200,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3304,7 +3296,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3331,12 +3323,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3346,47 +3338,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3416,7 +3408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,23 +3435,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3520,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3530,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,12 +3539,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3562,47 +3554,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3632,7 +3624,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3642,7 +3634,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,12 +3651,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3674,47 +3666,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3744,7 +3736,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3754,7 +3746,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,18 +3763,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3848,7 +3840,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3858,7 +3850,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3875,23 +3867,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3899,7 +3895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,23 +3979,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,23 +4083,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4107,7 +4111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4130,7 +4138,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4160,7 +4168,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4178,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,7 +4195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4195,15 +4203,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4211,7 +4223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4234,7 +4250,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4264,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4274,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,39 +4307,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4346,7 +4354,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4376,7 +4384,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4386,7 +4394,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4403,39 +4411,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,23 +4515,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4627,31 +4627,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4674,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4704,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,39 +4723,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4786,7 +4770,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4816,7 +4800,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4826,7 +4810,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,7 +4827,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4851,23 +4835,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4890,7 +4882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,12 +4939,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4962,39 +4954,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5002,7 +4994,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5032,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5042,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,27 +5051,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5087,26 +5075,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5114,7 +5098,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5144,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5154,7 +5138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5171,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5179,23 +5163,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5218,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,12 +5267,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5290,39 +5282,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5330,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,27 +5379,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5415,26 +5403,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5442,7 +5426,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5472,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5482,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5499,12 +5483,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5514,12 +5498,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5529,7 +5513,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5554,7 +5538,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5584,7 +5568,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5594,7 +5578,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5611,36 +5595,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -5658,7 +5650,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5688,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5698,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5715,7 +5707,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5723,19 +5715,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5743,11 +5731,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5770,7 +5754,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5800,7 +5784,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5810,7 +5794,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5827,7 +5811,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5835,23 +5819,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5874,7 +5866,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5904,7 +5896,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5906,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,31 +5923,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,36 +6035,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -6082,7 +6090,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6112,7 +6120,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6122,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,54 +6147,46 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6251,23 +6251,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6275,7 +6279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6298,7 +6306,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6328,7 +6336,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6338,7 +6346,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6355,39 +6363,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6478,17 +6478,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,39 +6571,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6626,7 +6618,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6656,7 +6648,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6666,7 +6658,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6683,12 +6675,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6698,22 +6690,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6723,27 +6715,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6768,17 +6760,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6795,7 +6787,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6803,31 +6795,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6835,27 +6819,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6880,17 +6864,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6907,12 +6891,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6922,12 +6906,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6937,32 +6921,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6992,7 +6976,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7002,7 +6986,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7019,27 +7003,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7047,26 +7027,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7074,7 +7050,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7104,7 +7080,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7114,7 +7090,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7131,12 +7107,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7146,12 +7122,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7161,7 +7137,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7171,27 +7147,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7216,17 +7192,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7243,31 +7219,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7275,27 +7259,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7320,17 +7304,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,31 +7331,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7379,27 +7371,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7424,17 +7416,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,31 +7443,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7555,31 +7555,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7602,7 +7610,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7632,7 +7640,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7642,7 +7650,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,23 +7667,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7683,7 +7695,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7691,27 +7707,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7736,17 +7752,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7763,39 +7779,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7803,27 +7811,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7848,17 +7856,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7875,54 +7883,46 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7987,7 +7987,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7995,31 +7995,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8042,7 +8034,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8072,7 +8064,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8082,7 +8074,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8099,7 +8091,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8107,31 +8099,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8154,7 +8138,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8184,7 +8168,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8194,7 +8178,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8211,7 +8195,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8222,17 +8206,17 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8258,7 +8242,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8288,7 +8272,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8298,7 +8282,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8315,31 +8299,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8347,27 +8339,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8392,17 +8384,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8419,12 +8411,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8434,22 +8426,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8474,7 +8466,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8504,7 +8496,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8514,7 +8506,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8531,7 +8523,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8546,22 +8538,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8586,7 +8578,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8616,7 +8608,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8626,7 +8618,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8643,7 +8635,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8658,22 +8650,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8698,7 +8690,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8728,7 +8720,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8738,7 +8730,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8755,39 +8747,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8810,7 +8794,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8840,7 +8824,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8850,7 +8834,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8867,39 +8851,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Degerfors IF</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8907,27 +8883,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8952,17 +8928,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8979,102 +8955,662 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
+          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IFK Göteborg -0.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785617556</t>
+          <t>1785628809</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>18.857143</t>
+          <t>21.361702</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
+          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.3089</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785617105</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.083673</t>
+          <t>24.767802</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
+          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>17.02796</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +783,11 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -779,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785616276</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32.338762</t>
+          <t>31.827963</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +867,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
+          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.9465</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.1763</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
+          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785616197</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>16.457143</t>
+          <t>45.086525</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
+          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,31 +979,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -995,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785615923</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12.203922</t>
+          <t>27.785915</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1075,31 +1083,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>15.45624</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>26.706246</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,31 +1187,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1234,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>44.94382</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1299,31 +1291,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.68448</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1346,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785625482</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>25.154494</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,27 +1387,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>18.14191</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.6088</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1431,11 +1411,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1488,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785625481</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>29.801906</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1523,23 +1499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.14247</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1547,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785620906</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>23.072479</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1634,7 +1618,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1644,12 +1628,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>IFK Göteborg -0.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1674,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,39 +1715,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1771,27 +1747,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1792,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,27 +1819,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1871,11 +1843,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1928,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,28 +1923,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2002,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2032,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,23 +2027,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2083,7 +2055,11 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2091,27 +2067,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2136,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,31 +2139,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2195,27 +2179,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2224,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2275,23 +2259,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2299,27 +2291,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2336,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,31 +2363,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2403,27 +2403,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2448,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,31 +2475,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2507,27 +2515,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,17 +2560,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2587,31 +2595,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2619,27 +2619,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2664,17 +2664,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2699,23 +2699,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2723,27 +2731,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2768,17 +2776,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,12 +2803,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2810,39 +2818,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AIK vs Orgryte IS</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>AIK</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>AIK vs Orgryte IS</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Orgryte IS</t>
@@ -2850,7 +2858,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2880,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2890,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2907,31 +2915,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2939,27 +2955,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +3000,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,7 +3027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3022,17 +3038,17 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3043,27 +3059,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3088,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,28 +3131,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3147,27 +3163,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,7 +3208,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3218,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,28 +3235,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3251,27 +3267,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3296,17 +3312,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,39 +3339,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3363,27 +3371,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3408,17 +3416,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,28 +3443,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3467,27 +3475,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3512,17 +3520,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,39 +3547,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3579,27 +3579,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,7 +3651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3666,22 +3666,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>AIK -2</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3691,27 +3691,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3736,17 +3736,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,23 +3763,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3795,27 +3795,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3840,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,12 +3867,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3882,22 +3882,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3907,27 +3907,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,28 +3979,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,39 +4083,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4123,27 +4115,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4168,17 +4160,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4195,39 +4187,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4235,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4280,17 +4264,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,18 +4291,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4384,7 +4368,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4394,7 +4378,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,31 +4395,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4458,7 +4450,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4488,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,23 +4507,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4592,7 +4584,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4594,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,7 +4611,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4627,23 +4619,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,31 +4723,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4770,7 +4778,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4800,7 +4808,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4810,7 +4818,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4827,39 +4835,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4954,22 +4954,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,23 +5051,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,12 +5155,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5170,22 +5170,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,12 +5267,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5282,22 +5282,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,23 +5379,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,27 +5483,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5511,26 +5507,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5568,7 +5560,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5570,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,27 +5587,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5623,26 +5611,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5680,7 +5664,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5674,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,7 +5691,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5718,7 +5702,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5784,7 +5768,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5794,7 +5778,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5811,7 +5795,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5819,19 +5803,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5839,26 +5819,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5896,7 +5872,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5906,7 +5882,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5923,12 +5899,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5938,39 +5914,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -5978,7 +5954,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6008,7 +5984,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6018,7 +5994,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,7 +6011,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6050,22 +6026,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6090,7 +6066,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6120,7 +6096,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6130,7 +6106,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,7 +6123,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6158,17 +6134,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6194,7 +6170,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6224,7 +6200,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6234,7 +6210,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6251,7 +6227,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6266,22 +6242,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6306,7 +6282,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6336,7 +6312,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6346,7 +6322,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6363,31 +6339,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6410,7 +6394,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6440,7 +6424,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6450,7 +6434,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6467,7 +6451,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6478,17 +6462,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6514,7 +6498,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6544,7 +6528,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6554,7 +6538,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6571,36 +6555,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -6618,7 +6610,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6648,7 +6640,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6658,7 +6650,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6675,12 +6667,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6690,12 +6682,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6760,7 +6752,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6770,7 +6762,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6787,18 +6779,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6864,7 +6856,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6874,7 +6866,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,12 +6883,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6906,12 +6898,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6921,7 +6913,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6946,7 +6938,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6976,7 +6968,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6986,7 +6978,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7003,23 +6995,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7027,7 +7023,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7219,39 +7219,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7259,27 +7251,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7304,17 +7296,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7331,12 +7323,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7346,22 +7338,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7371,27 +7363,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7416,17 +7408,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7443,62 +7435,54 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7528,7 +7512,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7538,7 +7522,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7555,54 +7539,46 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7610,7 +7586,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7640,7 +7616,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7650,7 +7626,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7667,39 +7643,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7707,27 +7675,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7752,17 +7720,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7779,23 +7747,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7803,7 +7775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7826,7 +7802,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7856,7 +7832,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7866,7 +7842,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7883,28 +7859,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7930,7 +7906,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7960,7 +7936,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7970,7 +7946,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7987,7 +7963,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7995,23 +7971,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8034,7 +8018,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8064,7 +8048,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8074,7 +8058,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8091,7 +8075,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8102,17 +8086,17 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8138,7 +8122,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8168,7 +8152,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8178,7 +8162,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8195,23 +8179,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8219,7 +8207,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8242,7 +8234,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8272,7 +8264,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8282,7 +8274,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8299,12 +8291,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8314,22 +8306,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>IFK Göteborg -1</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8339,27 +8331,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8384,17 +8376,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8411,12 +8403,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8426,22 +8418,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8451,27 +8443,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8496,17 +8488,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8523,12 +8515,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8538,22 +8530,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8578,7 +8570,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8608,7 +8600,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8618,7 +8610,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8635,12 +8627,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8650,22 +8642,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8690,7 +8682,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8720,7 +8712,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8730,7 +8722,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8747,31 +8739,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8779,27 +8779,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8824,17 +8824,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8851,7 +8851,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8862,17 +8862,17 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8955,39 +8955,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9010,7 +9002,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9040,7 +9032,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9050,7 +9042,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9067,7 +9059,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9075,31 +9067,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9122,7 +9106,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9152,7 +9136,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9162,7 +9146,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9179,7 +9163,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9187,31 +9171,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9234,7 +9210,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9264,7 +9240,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9274,7 +9250,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9291,39 +9267,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9346,7 +9314,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9376,7 +9344,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9386,7 +9354,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9403,12 +9371,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9418,47 +9386,47 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>Degerfors IF</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>IFK Göteborg</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Degerfors IF</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9488,7 +9456,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9498,7 +9466,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9515,102 +9483,1206 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>75.88</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.5587</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785542520</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>135.803132</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>9.76138</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785542512</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>23.241381</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.325</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785542511</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>9.353846</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2.99</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.1687</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785535711</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>17.718519</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>11.941176</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr">
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="V95" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
+          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>AIK -0.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
+          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785628809</t>
+          <t>1785630361</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>21.361702</t>
+          <t>15.009381</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
+          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17.35035</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>AIK -1.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>24.767802</t>
+          <t>41.310357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
+          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17.02796</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>AIK -2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31.827963</t>
+          <t>13.285714</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
+          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9465</t>
+          <t>13.86598</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1763</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>AIK -1</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630359</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>45.086525</t>
+          <t>24.871713</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
+          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -982,17 +990,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>18.65467</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630170</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>27.785915</t>
+          <t>31.484675</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
+          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1083,23 +1091,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.45624</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1107,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785628809</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>26.706246</t>
+          <t>21.361702</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
+          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,7 +1203,11 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1195,15 +1215,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1211,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>44.94382</t>
+          <t>24.767802</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
+          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,15 +1315,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.68448</t>
+          <t>17.02796</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1307,7 +1335,11 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1315,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785625482</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>25.154494</t>
+          <t>31.827963</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,28 +1419,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
+          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.14191</t>
+          <t>7.9465</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6088</t>
+          <t>1.1763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1434,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785625481</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.801906</t>
+          <t>45.086525</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
+          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1499,19 +1531,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.14247</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3962</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1519,11 +1547,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1531,27 +1555,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1600,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785620906</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>23.072479</t>
+          <t>27.785915</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
+          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1611,31 +1635,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>15.45624</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1643,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785617556</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>18.857143</t>
+          <t>26.706246</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
+          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.3089</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1747,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
+          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785617105</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.083673</t>
+          <t>44.94382</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,23 +1835,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
+          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>9.68448</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1896,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785616276</t>
+          <t>1785625482</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>32.338762</t>
+          <t>25.154494</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,28 +1939,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
+          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>18.14191</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.6088</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1955,27 +1971,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +2016,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785616197</t>
+          <t>1785625481</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>16.457143</t>
+          <t>29.801906</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
+          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2042,22 +2058,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>9.14247</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2082,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785615923</t>
+          <t>1785620906</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>12.203922</t>
+          <t>23.072479</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2154,22 +2170,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>IFK Göteborg -0.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2179,27 +2195,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2224,17 +2240,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,39 +2267,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2291,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,39 +2371,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,39 +2475,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2515,27 +2507,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2560,17 +2552,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,7 +2579,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2595,23 +2587,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2619,27 +2619,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2706,22 +2706,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2731,27 +2731,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,12 +2803,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,12 +2915,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2930,22 +2930,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +3027,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3035,23 +3035,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3059,27 +3067,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3104,17 +3112,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,28 +3139,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3178,7 +3186,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3216,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3226,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,31 +3243,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3267,27 +3283,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3312,7 +3328,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3338,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,31 +3355,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3371,27 +3395,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3440,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,31 +3467,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3475,27 +3507,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3520,17 +3552,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3547,28 +3579,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3579,27 +3611,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3624,7 +3656,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3634,7 +3666,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3651,39 +3683,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3691,27 +3715,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3736,17 +3760,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,28 +3787,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3795,27 +3819,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3840,17 +3864,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,7 +3891,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3875,59 +3899,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3952,17 +3968,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3979,28 +3995,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4026,7 +4042,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4056,7 +4072,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4066,7 +4082,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4083,28 +4099,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4130,7 +4146,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4160,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4170,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4187,7 +4203,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4195,23 +4211,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4219,27 +4243,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4264,17 +4288,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4291,23 +4315,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4323,27 +4347,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4368,17 +4392,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4395,12 +4419,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4410,22 +4434,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4435,27 +4459,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4480,17 +4504,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4507,28 +4531,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4539,27 +4563,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4584,17 +4608,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4611,7 +4635,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4619,31 +4643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4651,27 +4667,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4696,17 +4712,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4723,7 +4739,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4731,31 +4747,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4763,27 +4771,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4808,17 +4816,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4939,12 +4947,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4954,47 +4962,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5032,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5042,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,23 +5059,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5128,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,12 +5163,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5170,47 +5178,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5248,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5258,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,12 +5275,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5282,47 +5290,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5352,7 +5360,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5362,7 +5370,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5379,18 +5387,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5456,7 +5464,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5466,7 +5474,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5483,23 +5491,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5507,7 +5519,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5530,7 +5546,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5560,7 +5576,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5570,7 +5586,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5587,23 +5603,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5664,7 +5680,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5674,7 +5690,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5691,23 +5707,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5715,7 +5735,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5738,7 +5762,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5768,7 +5792,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5778,7 +5802,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5795,7 +5819,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5803,15 +5827,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5819,7 +5847,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5842,7 +5874,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5872,7 +5904,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5882,7 +5914,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5899,39 +5931,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5954,7 +5978,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5984,7 +6008,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5994,7 +6018,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6011,39 +6035,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6066,7 +6082,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6096,7 +6112,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6106,7 +6122,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,23 +6139,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6170,7 +6186,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6200,7 +6216,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6210,7 +6226,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6227,7 +6243,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6235,31 +6251,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6282,7 +6290,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6312,7 +6320,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6322,7 +6330,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6339,39 +6347,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6459,23 +6459,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6498,7 +6506,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6528,7 +6536,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,12 +6563,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6570,39 +6578,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -6610,7 +6618,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6640,7 +6648,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6650,7 +6658,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,27 +6675,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6695,26 +6699,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,7 +6779,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6787,23 +6787,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6826,7 +6834,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6856,7 +6864,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6866,7 +6874,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6883,12 +6891,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6898,39 +6906,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -6938,7 +6946,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6968,7 +6976,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6978,7 +6986,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6995,27 +7003,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7023,26 +7027,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7219,36 +7219,44 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -7266,7 +7274,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7296,7 +7304,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7306,7 +7314,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7323,7 +7331,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7331,19 +7339,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7351,11 +7355,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7443,23 +7443,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7482,7 +7490,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7512,7 +7520,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7522,7 +7530,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7539,31 +7547,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7586,7 +7602,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7616,7 +7632,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7626,7 +7642,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7643,36 +7659,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -7690,7 +7714,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7720,7 +7744,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7730,7 +7754,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7747,54 +7771,46 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7802,7 +7818,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7832,7 +7848,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7842,7 +7858,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7859,23 +7875,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7883,7 +7903,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7906,7 +7930,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7936,7 +7960,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7970,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,39 +7987,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8018,7 +8034,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8048,7 +8064,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8058,7 +8074,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,7 +8091,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8086,17 +8102,17 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8122,7 +8138,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8152,7 +8168,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8162,7 +8178,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8179,39 +8195,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8234,7 +8242,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8264,7 +8272,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8282,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,12 +8299,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8306,22 +8314,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -8331,27 +8339,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8376,17 +8384,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8403,7 +8411,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8411,31 +8419,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8443,27 +8443,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8515,12 +8515,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8627,27 +8627,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8655,26 +8651,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8682,7 +8674,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8712,7 +8704,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8722,7 +8714,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8739,12 +8731,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8754,12 +8746,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8769,7 +8761,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8779,27 +8771,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8824,17 +8816,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8851,31 +8843,39 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8883,27 +8883,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8928,17 +8928,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8955,31 +8955,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8987,27 +8995,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9032,17 +9040,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9059,31 +9067,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9106,7 +9122,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9136,7 +9152,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9146,7 +9162,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9163,31 +9179,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9210,7 +9234,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9240,7 +9264,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9250,7 +9274,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9267,23 +9291,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9291,7 +9319,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9299,27 +9331,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9344,17 +9376,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9371,39 +9403,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9411,27 +9435,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9456,17 +9480,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9483,54 +9507,46 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -9538,7 +9554,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9568,7 +9584,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9578,7 +9594,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9595,7 +9611,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9603,31 +9619,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9650,7 +9658,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9680,7 +9688,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9690,7 +9698,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9707,7 +9715,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9715,31 +9723,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9819,7 +9819,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9830,17 +9830,17 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9923,31 +9923,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9955,27 +9963,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10000,17 +10008,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10027,12 +10035,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10042,22 +10050,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -10082,7 +10090,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10112,7 +10120,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10122,7 +10130,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10139,7 +10147,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10154,22 +10162,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10194,7 +10202,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10224,7 +10232,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10234,7 +10242,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10251,7 +10259,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10266,22 +10274,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10306,7 +10314,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10336,7 +10344,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10346,7 +10354,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10363,39 +10371,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10475,39 +10475,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Degerfors IF</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10515,27 +10507,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10560,17 +10552,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10587,102 +10579,662 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T100" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
+          <t>0x183ade0b8727ea29844da0e8769ac25d6a6e61b7253c7c911aa8cb5fdfa37a57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,31 +539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9.38181</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>AIK -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785630361</t>
+          <t>1785638599</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15.009381</t>
+          <t>48.111846</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
+          <t>0x9ebb56c0a8c66d883fe6ba9596908c553a0729ed627be968ad4a1b913379cd50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,31 +643,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.35035</t>
+          <t>1.27326</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>AIK -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785630360</t>
+          <t>1785636154</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>41.310357</t>
+          <t>1.783902</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
+          <t>0x294363315446e5d09d65e25e2c1023ea62081a1635f41b97edd69948ed30f233</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>16.58096</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xbbb53205c1138e8d248944c8bbaca41bc9ae83832ff137d12a88f5a2e8054ebd</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785630360</t>
+          <t>1785636154</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.285714</t>
+          <t>27.070955</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,39 +843,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
+          <t>0x8180f54c50443af98d0d394ec0a0e63cd54bd90d83da91e97dfe0a383810cc7d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.86598</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AIK -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -907,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785630359</t>
+          <t>1785636153</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>24.871713</t>
+          <t>60.469352</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
+          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -987,23 +955,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.65467</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AIK -0.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1026,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785630170</t>
+          <t>1785630361</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>31.484675</t>
+          <t>15.009381</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
+          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1098,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>17.35035</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>AIK -1.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785628809</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>21.361702</t>
+          <t>41.310357</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
+          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1210,22 +1186,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>AIK -2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>24.767802</t>
+          <t>13.285714</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
+          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.02796</t>
+          <t>13.86598</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>AIK -1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630359</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31.827963</t>
+          <t>24.871713</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
+          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1430,17 +1406,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.9465</t>
+          <t>18.65467</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1763</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1466,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1496,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630170</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>45.086525</t>
+          <t>31.484675</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
+          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1531,23 +1507,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1555,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785628809</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>27.785915</t>
+          <t>21.361702</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
+          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1635,23 +1619,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.45624</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1659,27 +1651,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1696,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>26.706246</t>
+          <t>24.767802</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
+          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,23 +1731,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17.02796</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1763,27 +1763,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>44.94382</t>
+          <t>31.827963</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
+          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1846,17 +1846,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.68448</t>
+          <t>7.9465</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.1763</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785625482</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>25.154494</t>
+          <t>45.086525</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,28 +1939,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
+          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.14191</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6088</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785625481</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>29.801906</t>
+          <t>27.785915</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
+          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2051,31 +2051,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.14247</t>
+          <t>15.45624</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3962</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2083,27 +2075,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2128,17 +2120,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785620906</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>23.072479</t>
+          <t>26.706246</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
+          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,31 +2155,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2195,27 +2179,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2240,17 +2224,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785617556</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>18.857143</t>
+          <t>44.94382</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,28 +2251,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
+          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.3089</t>
+          <t>9.68448</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2299,27 +2283,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2328,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785617105</t>
+          <t>1785625482</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.083673</t>
+          <t>25.154494</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,28 +2355,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
+          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>18.14191</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.6088</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2418,7 +2402,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785616276</t>
+          <t>1785625481</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2442,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>32.338762</t>
+          <t>29.801906</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,31 +2459,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
+          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>9.14247</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2507,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,7 +2544,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785616197</t>
+          <t>1785620906</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2554,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>16.457143</t>
+          <t>23.072479</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2594,22 +2586,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>IFK Göteborg -0.5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2634,7 +2626,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2664,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785615923</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>12.203922</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,39 +2683,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2731,27 +2715,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2776,17 +2760,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,39 +2787,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2858,7 +2834,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2888,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,39 +2891,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2955,27 +2923,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3000,17 +2968,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,7 +2995,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3042,12 +3010,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3067,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3112,17 +3080,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3139,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3147,23 +3115,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3171,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3216,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3243,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3258,22 +3234,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3283,27 +3259,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3328,17 +3304,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3355,12 +3331,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3370,22 +3346,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3410,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3440,7 +3416,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3450,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3467,12 +3443,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3482,22 +3458,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3522,7 +3498,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3552,7 +3528,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3562,7 +3538,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3579,7 +3555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3590,17 +3566,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3626,7 +3602,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3656,7 +3632,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3666,7 +3642,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3683,31 +3659,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3715,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3760,7 +3744,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3770,7 +3754,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3787,31 +3771,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3819,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3864,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3891,31 +3883,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3923,27 +3923,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,28 +3995,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4027,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,28 +4099,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4131,27 +4131,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,39 +4203,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4243,27 +4235,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,17 +4280,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,7 +4307,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4326,17 +4318,17 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4347,27 +4339,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4392,17 +4384,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,67 +4411,59 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4504,17 +4488,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4531,28 +4515,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4578,7 +4562,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4608,7 +4592,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4618,7 +4602,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4635,7 +4619,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4643,23 +4627,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4667,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4712,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4739,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4750,17 +4742,17 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4771,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,31 +4835,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4875,27 +4875,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,27 +4947,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4975,11 +4971,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4987,27 +4979,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5032,17 +5024,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,28 +5051,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5091,27 +5083,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,17 +5128,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,7 +5155,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5171,31 +5163,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5203,27 +5187,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5248,17 +5232,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,39 +5259,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5330,7 +5306,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5336,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5346,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,31 +5363,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5434,7 +5418,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5464,7 +5448,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5474,7 +5458,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,27 +5475,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5519,34 +5499,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5576,7 +5552,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5586,7 +5562,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5603,31 +5579,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5650,7 +5634,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5680,7 +5664,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5690,7 +5674,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5707,12 +5691,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5722,47 +5706,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5792,7 +5776,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5802,7 +5786,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5819,27 +5803,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5847,34 +5827,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5904,7 +5880,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5914,7 +5890,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5931,23 +5907,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5955,7 +5935,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5978,7 +5962,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6008,7 +5992,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6018,7 +6002,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6035,23 +6019,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6112,7 +6096,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6122,7 +6106,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,23 +6123,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6163,7 +6151,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6186,7 +6178,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6216,7 +6208,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6226,7 +6218,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6243,23 +6235,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6267,7 +6263,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6347,7 +6347,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6358,12 +6358,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6451,39 +6451,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6506,7 +6498,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6536,7 +6528,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6546,7 +6538,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6563,39 +6555,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6618,7 +6602,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6648,7 +6632,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6658,7 +6642,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6675,7 +6659,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6686,12 +6670,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6722,7 +6706,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6752,7 +6736,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6762,7 +6746,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6779,39 +6763,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6834,7 +6810,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6864,7 +6840,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6874,7 +6850,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6891,7 +6867,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6906,22 +6882,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6946,7 +6922,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6976,7 +6952,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6986,7 +6962,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7003,7 +6979,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7011,23 +6987,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7050,7 +7034,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7080,7 +7064,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7090,7 +7074,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7107,27 +7091,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7135,26 +7115,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7162,7 +7138,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7192,7 +7168,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7202,7 +7178,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7219,12 +7195,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7234,39 +7210,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7274,7 +7250,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7304,7 +7280,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7314,7 +7290,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7331,7 +7307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7339,23 +7315,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7378,7 +7362,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7408,7 +7392,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7418,7 +7402,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7435,27 +7419,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7463,26 +7443,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7490,7 +7466,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7520,7 +7496,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7530,7 +7506,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7547,12 +7523,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7562,12 +7538,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7632,7 +7608,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7642,7 +7618,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7659,12 +7635,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7674,12 +7650,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7689,7 +7665,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7714,7 +7690,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7744,7 +7720,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7754,7 +7730,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7771,7 +7747,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7782,17 +7758,17 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -7818,7 +7794,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7848,7 +7824,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7858,7 +7834,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7875,12 +7851,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7890,12 +7866,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7905,7 +7881,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7930,7 +7906,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7960,7 +7936,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7970,7 +7946,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7987,7 +7963,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7995,23 +7971,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8034,7 +8018,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8064,7 +8048,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8074,7 +8058,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8091,7 +8075,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8099,23 +8083,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8138,7 +8130,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8168,7 +8160,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8178,7 +8170,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8195,18 +8187,18 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8242,7 +8234,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8272,7 +8264,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8282,7 +8274,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8299,12 +8291,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8314,12 +8306,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8329,24 +8321,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8354,7 +8346,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8384,7 +8376,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8394,7 +8386,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8411,7 +8403,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8422,17 +8414,17 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8458,7 +8450,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8488,7 +8480,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8498,7 +8490,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8515,7 +8507,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8523,31 +8515,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8570,7 +8554,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8600,7 +8584,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8610,7 +8594,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8627,28 +8611,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8674,7 +8658,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8704,7 +8688,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8714,7 +8698,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8731,12 +8715,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8746,12 +8730,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8761,7 +8745,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8786,7 +8770,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8816,7 +8800,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8826,7 +8810,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8843,39 +8827,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8883,27 +8859,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8928,17 +8904,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8955,12 +8931,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8970,22 +8946,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8995,27 +8971,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -9040,17 +9016,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9067,27 +9043,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9095,34 +9067,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9152,7 +9120,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9162,7 +9130,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9179,12 +9147,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9194,12 +9162,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9209,24 +9177,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -9234,7 +9202,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9264,7 +9232,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9274,7 +9242,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9291,12 +9259,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9306,22 +9274,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9331,27 +9299,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9376,17 +9344,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9403,31 +9371,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9435,27 +9411,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9480,17 +9456,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9507,31 +9483,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9554,7 +9538,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9584,7 +9568,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9594,7 +9578,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9611,31 +9595,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9658,7 +9650,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9688,7 +9680,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9698,7 +9690,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9715,31 +9707,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9747,27 +9747,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9819,7 +9819,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9830,7 +9830,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9923,39 +9923,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9963,27 +9955,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -10008,17 +10000,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10035,54 +10027,46 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -10090,7 +10074,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10120,7 +10104,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10130,7 +10114,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10147,7 +10131,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10155,31 +10139,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10202,7 +10178,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10232,7 +10208,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10242,7 +10218,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10259,7 +10235,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10267,31 +10243,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10314,7 +10282,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10344,7 +10312,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10354,7 +10322,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10371,31 +10339,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -1</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10403,27 +10379,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -10448,17 +10424,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10475,31 +10451,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10522,7 +10506,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10552,7 +10536,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10562,7 +10546,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10579,12 +10563,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10594,12 +10578,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10664,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10674,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10691,7 +10675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10706,22 +10690,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10746,7 +10730,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10776,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10786,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10803,7 +10787,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10811,31 +10795,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10858,7 +10834,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10888,7 +10864,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10898,7 +10874,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10915,39 +10891,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10970,7 +10938,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11000,7 +10968,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11010,7 +10978,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11027,12 +10995,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11042,22 +11010,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11067,27 +11035,27 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -11112,17 +11080,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>45.969789</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11139,102 +11107,550 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr">
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U104" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="V104" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x183ade0b8727ea29844da0e8769ac25d6a6e61b7253c7c911aa8cb5fdfa37a57</t>
+          <t>0x2710693e45dc8b9ebb20e22959d826cce242249a9c323a655c8844ac92853d17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.38181</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785638599</t>
+          <t>1785643124</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>48.111846</t>
+          <t>21.333333</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9ebb56c0a8c66d883fe6ba9596908c553a0729ed627be968ad4a1b913379cd50</t>
+          <t>0x183ade0b8727ea29844da0e8769ac25d6a6e61b7253c7c911aa8cb5fdfa37a57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,17 +654,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.27326</t>
+          <t>9.38181</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785636154</t>
+          <t>1785638599</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.783902</t>
+          <t>48.111846</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x294363315446e5d09d65e25e2c1023ea62081a1635f41b97edd69948ed30f233</t>
+          <t>0x9ebb56c0a8c66d883fe6ba9596908c553a0729ed627be968ad4a1b913379cd50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.58096</t>
+          <t>1.27326</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xbbb53205c1138e8d248944c8bbaca41bc9ae83832ff137d12a88f5a2e8054ebd</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>27.070955</t>
+          <t>1.783902</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8180f54c50443af98d0d394ec0a0e63cd54bd90d83da91e97dfe0a383810cc7d</t>
+          <t>0x294363315446e5d09d65e25e2c1023ea62081a1635f41b97edd69948ed30f233</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>16.58096</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -890,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
+          <t>0xbbb53205c1138e8d248944c8bbaca41bc9ae83832ff137d12a88f5a2e8054ebd</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785636153</t>
+          <t>1785636154</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>60.469352</t>
+          <t>27.070955</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
+          <t>0x8180f54c50443af98d0d394ec0a0e63cd54bd90d83da91e97dfe0a383810cc7d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -955,31 +963,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AIK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -987,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785630361</t>
+          <t>1785636153</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15.009381</t>
+          <t>60.469352</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
+          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17.35035</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AIK -1.5</t>
+          <t>AIK -0.5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785630360</t>
+          <t>1785630361</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>41.310357</t>
+          <t>15.009381</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
+          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>17.35035</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AIK -2</t>
+          <t>AIK -1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13.285714</t>
+          <t>41.310357</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
+          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.86598</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>AIK -1</t>
+          <t>AIK -2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785630359</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>24.871713</t>
+          <t>13.285714</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,31 +1395,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
+          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.65467</t>
+          <t>13.86598</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AIK -1</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1442,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785630170</t>
+          <t>1785630359</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>31.484675</t>
+          <t>24.871713</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
+          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1507,31 +1515,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>18.65467</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1539,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785628809</t>
+          <t>1785630170</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>21.361702</t>
+          <t>31.484675</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
+          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1651,27 +1651,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785628809</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>24.767802</t>
+          <t>21.361702</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
+          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17.02796</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>31.827963</t>
+          <t>24.767802</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
+          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1843,23 +1843,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.9465</t>
+          <t>17.02796</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.1763</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1867,27 +1875,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1912,17 +1920,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>45.086525</t>
+          <t>31.827963</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
+          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1950,17 +1958,17 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>7.9465</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.1763</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1986,7 +1994,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>27.785915</t>
+          <t>45.086525</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2051,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
+          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2054,17 +2062,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.45624</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2090,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>26.706246</t>
+          <t>27.785915</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
+          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,17 +2166,17 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.45624</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>44.94382</t>
+          <t>26.706246</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
+          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2262,17 +2270,17 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.68448</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2298,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785625482</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>25.154494</t>
+          <t>44.94382</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,28 +2363,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
+          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.14191</t>
+          <t>9.68448</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6088</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2402,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2432,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785625481</t>
+          <t>1785625482</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>29.801906</t>
+          <t>25.154494</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,39 +2467,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
+          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.14247</t>
+          <t>18.14191</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3962</t>
+          <t>1.6088</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2499,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785620906</t>
+          <t>1785625481</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>23.072479</t>
+          <t>29.801906</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
+          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2586,22 +2586,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>9.14247</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IFK Göteborg -0.5</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785617556</t>
+          <t>1785620906</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>18.857143</t>
+          <t>23.072479</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,31 +2683,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.3089</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>IFK Göteborg -0.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785617105</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2770,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>3.083673</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,28 +2795,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2819,27 +2827,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2864,17 +2872,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785616276</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>32.338762</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2899,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2902,17 +2910,17 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2923,27 +2931,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2976,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785616197</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>16.457143</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,39 +3003,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3035,27 +3035,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785615923</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>12.203922</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3122,22 +3122,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,7 +3219,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3234,22 +3234,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3346,22 +3346,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3458,22 +3458,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3563,23 +3563,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3587,27 +3595,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3632,17 +3640,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,7 +3667,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3667,31 +3675,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3699,27 +3699,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3811,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,31 +3995,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4027,27 +4035,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4072,17 +4080,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,28 +4107,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4146,7 +4154,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4176,7 +4184,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4194,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,23 +4211,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4280,7 +4288,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4298,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,18 +4315,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4384,7 +4392,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4394,7 +4402,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,28 +4419,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4443,27 +4451,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4488,7 +4496,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4498,7 +4506,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4515,7 +4523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4526,17 +4534,17 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4562,7 +4570,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4592,7 +4600,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4602,7 +4610,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4619,39 +4627,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4659,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4739,23 +4739,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4778,7 +4786,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4808,7 +4816,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4826,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,7 +4843,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4843,46 +4851,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AIK vs Orgryte IS</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>AIK</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>AIK vs Orgryte IS</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>Orgryte IS</t>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4955,23 +4955,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4979,27 +4987,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5024,17 +5032,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,7 +5059,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5062,17 +5070,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5098,7 +5106,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5128,7 +5136,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5138,7 +5146,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5155,7 +5163,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5166,17 +5174,17 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5202,7 +5210,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5232,7 +5240,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5242,7 +5250,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5259,28 +5267,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5291,27 +5299,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5336,17 +5344,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5363,39 +5371,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,31 +5475,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5522,7 +5530,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5552,7 +5560,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5562,7 +5570,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5579,39 +5587,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,31 +5803,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5850,7 +5858,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5880,7 +5888,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5890,7 +5898,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5907,7 +5915,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5915,11 +5923,7 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>5</t>
@@ -5927,7 +5931,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5935,34 +5939,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6019,23 +6019,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6043,7 +6047,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6066,7 +6074,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6096,7 +6104,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6106,7 +6114,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,27 +6131,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6151,34 +6155,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6347,7 +6347,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6355,15 +6355,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6371,7 +6375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6394,7 +6402,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6434,7 +6442,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6451,7 +6459,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6462,12 +6470,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6555,18 +6563,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6642,7 +6650,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6659,18 +6667,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6736,7 +6744,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6746,7 +6754,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6763,18 +6771,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6840,7 +6848,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6850,7 +6858,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6867,39 +6875,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7091,7 +7091,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7099,23 +7099,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7138,7 +7146,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7178,7 +7186,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7195,7 +7203,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7203,31 +7211,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7307,7 +7307,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7427,23 +7427,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7466,7 +7474,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7496,7 +7504,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7506,7 +7514,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7523,27 +7531,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7551,26 +7555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7635,12 +7635,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7747,23 +7747,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7771,7 +7775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7834,7 +7842,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7851,27 +7859,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7879,26 +7883,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,12 +8075,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,7 +8187,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8195,28 +8195,36 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -8234,7 +8242,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8264,7 +8272,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8274,7 +8282,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8291,7 +8299,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8299,31 +8307,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8403,31 +8403,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8450,7 +8458,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8480,7 +8488,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8490,7 +8498,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8507,28 +8515,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8554,7 +8562,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8594,7 +8602,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8611,28 +8619,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8658,7 +8666,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8698,7 +8706,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8715,54 +8723,46 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8827,23 +8827,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8851,7 +8855,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8904,7 +8912,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8914,7 +8922,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8931,27 +8939,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -8959,11 +8963,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9051,15 +9051,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9067,7 +9071,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9120,7 +9128,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9130,7 +9138,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9147,27 +9155,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9175,11 +9179,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9259,12 +9259,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9274,22 +9274,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9299,27 +9299,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9344,17 +9344,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9371,12 +9371,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9483,12 +9483,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9498,22 +9498,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9523,27 +9523,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9568,17 +9568,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9595,12 +9595,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9625,24 +9625,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9707,12 +9707,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9747,27 +9747,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9819,23 +9819,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9843,7 +9847,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9851,27 +9859,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9896,17 +9904,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9923,7 +9931,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9934,17 +9942,17 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -9970,7 +9978,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10000,7 +10008,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10010,7 +10018,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10027,7 +10035,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10038,7 +10046,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10104,7 +10112,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10114,7 +10122,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10131,7 +10139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10142,17 +10150,17 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -10178,7 +10186,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10218,7 +10226,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10235,7 +10243,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10246,17 +10254,17 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10282,7 +10290,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10312,7 +10320,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10322,7 +10330,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10339,39 +10347,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10379,27 +10379,27 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -10424,17 +10424,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10451,12 +10451,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10466,22 +10466,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10491,27 +10491,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10536,17 +10536,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,12 +10563,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10578,22 +10578,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10675,7 +10675,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10690,22 +10690,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bk Hacken -1.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10787,7 +10787,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10795,23 +10795,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10834,7 +10842,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10864,7 +10872,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10874,7 +10882,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10891,7 +10899,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10902,12 +10910,12 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10968,7 +10976,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10978,7 +10986,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10995,39 +11003,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>11.941176</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11107,12 +11107,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -11122,22 +11122,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785534359</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>45.969789</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11219,7 +11219,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11234,22 +11234,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>3.80999</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785533370</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>6.047603</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11331,12 +11331,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11346,22 +11346,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.405</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785531926</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>13.555556</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11443,7 +11443,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11458,22 +11458,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>22.74</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11483,27 +11483,27 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -11528,17 +11528,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785494939</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>54.960725</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11555,102 +11555,214 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>1.4675</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr">
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="T105" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="U105" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
+      <c r="V105" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Allsvenskan/trades.xlsx
+++ b/data/sxbet/ligas/Allsvenskan/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x2710693e45dc8b9ebb20e22959d826cce242249a9c323a655c8844ac92853d17</t>
+          <t>0x0b886c21b764bbd0bf64527a2f7011d410e785cc9c482b27d79ac6b3aa9de400</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,31 +539,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.00154</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4688</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785643124</t>
+          <t>1785649278</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>21.333333</t>
+          <t>0.00348</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x183ade0b8727ea29844da0e8769ac25d6a6e61b7253c7c911aa8cb5fdfa37a57</t>
+          <t>0xefece7fe4e3e0b949224d479645f908c21c764f7bf174d69c8ad1af0fd7344c5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -654,17 +646,17 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.38181</t>
+          <t>14.17999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -675,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785638599</t>
+          <t>1785649277</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>48.111846</t>
+          <t>24.501063</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9ebb56c0a8c66d883fe6ba9596908c553a0729ed627be968ad4a1b913379cd50</t>
+          <t>0xcfcef122c4cff9807e952c66d7ee28a42f479b9c0ee82d5c92e389bd05d3d00f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.27326</t>
+          <t>19.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7138</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -779,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785636154</t>
+          <t>1785646134</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.783902</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x294363315446e5d09d65e25e2c1023ea62081a1635f41b97edd69948ed30f233</t>
+          <t>0x52f2a531ebbfe4c09c02d4b36fbdf91482f1f2e0079e8c2fb62a886df3014b7a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.58096</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Allsvenskan</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xbbb53205c1138e8d248944c8bbaca41bc9ae83832ff137d12a88f5a2e8054ebd</t>
+          <t>0xa0b899a75cd0aa5ccb7dce40c57f9bc20e569cd59432523a8efc81705e3d7c83</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785636154</t>
+          <t>1785646059</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>27.070955</t>
+          <t>18.823529</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8180f54c50443af98d0d394ec0a0e63cd54bd90d83da91e97dfe0a383810cc7d</t>
+          <t>0x658bf2b477af5aad59c96ec72d9c950780c35bdef4e90436ab62e1e881a0876e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,7 +958,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>24.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785636153</t>
+          <t>1785644834</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>60.469352</t>
+          <t>33.751313</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
+          <t>0xd426fd0e1a74622c143746bdc66ad6e562baa2d98bff8b96b0e5de5aa9d989a5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1067,31 +1059,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20.31997</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6663</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AIK -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1099,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785630361</t>
+          <t>1785643520</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15.009381</t>
+          <t>25.439712</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1155,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
+          <t>0x2710693e45dc8b9ebb20e22959d826cce242249a9c323a655c8844ac92853d17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,22 +1170,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.35035</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4688</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AIK -1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1211,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785630360</t>
+          <t>1785643124</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>41.310357</t>
+          <t>21.333333</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1267,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
+          <t>0x183ade0b8727ea29844da0e8769ac25d6a6e61b7253c7c911aa8cb5fdfa37a57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,31 +1275,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>9.38181</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1323,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785630360</t>
+          <t>1785638599</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.285714</t>
+          <t>48.111846</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,39 +1371,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
+          <t>0x9ebb56c0a8c66d883fe6ba9596908c553a0729ed627be968ad4a1b913379cd50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.86598</t>
+          <t>1.27326</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>AIK -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1435,27 +1403,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1448,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785630359</t>
+          <t>1785636154</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>24.871713</t>
+          <t>1.783902</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,28 +1475,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
+          <t>0x294363315446e5d09d65e25e2c1023ea62081a1635f41b97edd69948ed30f233</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.65467</t>
+          <t>16.58096</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1539,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
+          <t>0xbbb53205c1138e8d248944c8bbaca41bc9ae83832ff137d12a88f5a2e8054ebd</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785630170</t>
+          <t>1785636154</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>31.484675</t>
+          <t>27.070955</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
+          <t>0x8180f54c50443af98d0d394ec0a0e63cd54bd90d83da91e97dfe0a383810cc7d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,31 +1587,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.7138</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1666,7 +1626,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
+          <t>0x86c9299274d20d9bf6a20929d30db9d81a99fdb61dae258a53965964d2023e67</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1656,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785628809</t>
+          <t>1785636153</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1666,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>21.361702</t>
+          <t>60.469352</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,7 +1683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
+          <t>0x20a324b099a1537a9738f770c9fb5d6e118de208ad1be8a053243df77e5dbd03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1743,17 +1703,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4038</t>
+          <t>1.6663</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>AIK -0.5</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1763,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
+          <t>0x4e788626bbbea711926f0ee0fe65d295398d4c8257f4ae85b4556669e829088f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1808,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630361</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24.767802</t>
+          <t>15.009381</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
+          <t>0xa16fbaafcde7996b0fe606465124ef15dc04c0f2b9984ad6a37128041246e71f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1850,22 +1810,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.02796</t>
+          <t>17.35035</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>AIK -1.5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1875,27 +1835,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1880,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785627441</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>31.827963</t>
+          <t>41.310357</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,7 +1907,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
+          <t>0x0e30e22c2948cbc90c7c432aefa6bde53565a55b8742a81022e7bd3e383e5693</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1955,23 +1915,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.9465</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1763</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -1994,7 +1962,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630360</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>45.086525</t>
+          <t>13.285714</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,23 +2019,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
+          <t>0x9ea5d06b2d1d02a8a463f96874f143efe63aadcc7aa896b3c7fa5d244e7bb5a0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.33</t>
+          <t>13.86598</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2075,7 +2047,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>AIK -1</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2128,7 +2104,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630359</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2114,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>27.785915</t>
+          <t>24.871713</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
+          <t>0x794b2b1690dafa93c42e3e874714f342e70153ec192ee07c406a8103806df40f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2166,12 +2142,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.45624</t>
+          <t>18.65467</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2232,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785630170</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>26.706246</t>
+          <t>31.484675</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
+          <t>0x297a148d2af2fa9e12ad91cd3496dfba2189c06f4ee1aeb905abb276a352834f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,23 +2243,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2225</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2291,27 +2275,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
+          <t>0x2481d201f873f473dc33617c78fc1596d7a290c5320eef392c80443c2a483a81</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2320,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785625483</t>
+          <t>1785628809</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>44.94382</t>
+          <t>21.361702</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2347,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
+          <t>0x9c18b2a384d425d6f7b1454825b9fb0a91147d4c643b25152f1f8e03432e0dba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2371,23 +2355,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.68448</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2395,27 +2387,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xb414c023d23917d0778df0bdbe5b67eb5d82b4a1898df9b687b3140a5e27ee0e</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2440,17 +2432,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785625482</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>25.154494</t>
+          <t>24.767802</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,31 +2459,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
+          <t>0x6fbceb31cb96af7ec94fc9106bb9057d77fde8cd6c48153606af8c7db6f1f082</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18.14191</t>
+          <t>17.02796</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6088</t>
+          <t>1.535</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2499,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785625481</t>
+          <t>1785627441</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>29.801906</t>
+          <t>31.827963</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
+          <t>0xa5b8a57eb5dd9cc568a018f45075093b3aad628dc867069a1fc2cd97341b6e42</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2579,31 +2579,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9.14247</t>
+          <t>7.9465</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3962</t>
+          <t>1.1763</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2611,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x40db17dfe952b0a0326de035af81bf2e583d13d7bb7f78dc0aa8060e49dfa1a4</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785620906</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>23.072479</t>
+          <t>45.086525</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,7 +2675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
+          <t>0x8840b232e1ef1313300e67fd500f29f6eaf993774fc928f7189b076db3a710cc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2691,31 +2683,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>12.33</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>IFK Göteborg -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -2723,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x511f7a11535c74eec3c2808b54b15506129424431854a13299c720896a0c1b35</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2768,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785617556</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>18.857143</t>
+          <t>27.785915</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,28 +2779,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
+          <t>0x81d93a2fa80a4e0bf4a6cc47ae3435eb3fc82c3c6ba7be4f4af52d833299864e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.3089</t>
+          <t>15.45624</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7488</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2827,27 +2811,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
+          <t>0x91d5c929bac039e0779eec9681e4e40ab3c5a2d1d185c20d777756c3ea80d0a5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2872,17 +2856,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785617105</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>3.083673</t>
+          <t>26.706246</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,28 +2883,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
+          <t>0x3c1f7a82c0eca02acbb64fb6b5ea430e625d3594cf4f26fbe48ff972b1edfd36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12.41</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3838</t>
+          <t>1.2225</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2946,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0x5c7665464e1b6e58d1efbb4d1aaee6788d89bda521bd8135cd064e98f62a9405</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785616276</t>
+          <t>1785625483</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>32.338762</t>
+          <t>44.94382</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,28 +2987,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
+          <t>0x185bbc1341051a1b2125e70acafb9c5cda66ba79e386d893bde29716b1c5ab65</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>9.68448</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.385</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3035,27 +3019,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3080,17 +3064,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785616197</t>
+          <t>1785625482</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16.457143</t>
+          <t>25.154494</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,27 +3091,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
+          <t>0x9d4d4e461900065ea8e7b5bd3f1e83fb2a6b31515c0e7cb73e98354e452474a5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>18.14191</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.6088</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3135,11 +3115,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3147,27 +3123,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3192,17 +3168,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785615923</t>
+          <t>1785625481</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12.203922</t>
+          <t>29.801906</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,7 +3195,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
+          <t>0xb2cc41e1f6b60b60629f98f434c44bf06f82ea6d52dc3ce365afe90c5915e67d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3234,22 +3210,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>9.14247</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5162</t>
+          <t>1.3962</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3259,27 +3235,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3304,17 +3280,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785620906</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>11.079903</t>
+          <t>23.072479</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,7 +3307,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
+          <t>0x0d1801b7ff0b7582e726ec766c40dff9134916e1c4a6b9c002c0a67f660887cd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3346,22 +3322,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>IFK Göteborg -0.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3371,27 +3347,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3416,17 +3392,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785610531</t>
+          <t>1785617556</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13.590909</t>
+          <t>18.857143</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,39 +3419,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
+          <t>0x0e4020ed82d8cc8444f3e29fbe158a4d4ecc18a84583290695b9509b3e325f12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.3089</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.2675</t>
+          <t>1.7488</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3483,27 +3451,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
+          <t>0xc573649b9b8cfe8a5bd7a1bd300a2ced395527c6fc38ec4a52387713a8871353</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3528,17 +3496,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785617105</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12.71028</t>
+          <t>3.083673</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,39 +3523,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
+          <t>0x1a1b839fc547ef37e72e0c8a72213f5306bcde04c7985592ac7b9ea87c7b3e02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>12.41</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4013</t>
+          <t>1.3838</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -3610,7 +3570,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3640,7 +3600,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785610530</t>
+          <t>1785616276</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3650,7 +3610,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10.641745</t>
+          <t>32.338762</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,28 +3627,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
+          <t>0xbce62c1b955e91357a459acace9c8176987f541d0889a74d2e6735c1687b1423</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3714,7 +3674,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
+          <t>0x5893395b67fbf986e3f8b621f276ff393640d4b442c47a29041f3a3bf8938acb</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3744,7 +3704,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785610047</t>
+          <t>1785616197</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3754,7 +3714,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>18.522167</t>
+          <t>16.457143</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3771,7 +3731,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
+          <t>0xef40abfc5ba39ff9a7025de6c5ce305c816d43fb120ddcf03573fb9e26a68531</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3786,22 +3746,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3826,7 +3786,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
+          <t>0x7b606f263125735c03c892897f2e5beddeae37a43c5c4b4c71aae42c2bbd6832</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3856,7 +3816,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785609745</t>
+          <t>1785615923</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3866,7 +3826,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>34.230415</t>
+          <t>12.203922</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,12 +3843,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
+          <t>0x9f6d342f0eef7ec20b46f7ee805195f6e97ac06b72865d7e5d23ebeca65eaa85</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3898,22 +3858,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.625</t>
+          <t>1.5162</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3938,7 +3898,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xfcc7a871901991d523808949aa0fa8949b3df3cefd57ce59713eca4358d0da41</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3968,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785607706</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3978,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>11.079903</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,12 +3955,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
+          <t>0x7e582c5e0ba141ea2d637f9dc81c95acea98edeef8a2713393b9b2e30225323b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4010,22 +3970,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.58999</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6225</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4050,7 +4010,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
+          <t>0xb8bd0f2ce4753a49832379ef2ca4247d24248fe5b1d85e1300fc59696b516cf7</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4080,7 +4040,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785607696</t>
+          <t>1785610531</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4090,7 +4050,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>31.469863</t>
+          <t>13.590909</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4107,7 +4067,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
+          <t>0xb7fbf0992f261acd9a5ba3ccde6135d62ad377a176eb15cf96a426bdbc2b8b6c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4115,23 +4075,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1.2675</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4139,27 +4107,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
+          <t>0x1bacdf138c9e091c33a6bb098abdaac92ff8eed3b6c5aba1ce65c598f1547836</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4184,17 +4152,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785606822</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>29.538462</t>
+          <t>12.71028</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4211,23 +4179,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
+          <t>0x41efefae67f324062ad5b1ca5039f72959b2094de18406dc40fd4844211fc1f8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.4013</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4235,7 +4207,11 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4243,27 +4219,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x5456505d6b8f6abc82f18f1164b28851210c45de632a436f54e05bc9f52f7840</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4288,17 +4264,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785604388</t>
+          <t>1785610530</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7.782101</t>
+          <t>10.641745</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4315,28 +4291,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
+          <t>0x1c163ff51a01cc9c5ecc6a8e0ae6f56d7234a2d1021e6a6cbeac6084699887c9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.21556</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4362,7 +4338,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0xc125c07ef9c509d122b83abe6b98e02f59cf91c3d36e15ce3ece334eff19faf7</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4392,7 +4368,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785604383</t>
+          <t>1785610047</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4402,7 +4378,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17.524313</t>
+          <t>18.522167</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4419,7 +4395,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
+          <t>0x8eb9f48f5362e8ba2b5b4aeaad13a3436f76513bd7727337cc199b1ffccac223</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4427,23 +4403,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4451,27 +4435,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna vs Malmo FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>IF Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
+          <t>0x9accad00fd2391cdcb81b6d30527aa5aa9e8c2fe4cb15de3e2fdf85fa84b4e94</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19611635</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4496,7 +4480,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785604382</t>
+          <t>1785609745</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4490,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>17.78125</t>
+          <t>34.230415</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,31 +4507,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
+          <t>0xacb8b406ab153121c2bd2e307b18968dd0ea0e993335e5238d4ea43e8e910fb2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.625</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4555,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4600,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785603319</t>
+          <t>1785607706</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>15.505376</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,31 +4619,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
+          <t>0x57656632cf7910f2e1b5527f8b27145e9847e2434970036131db954ece3fcea7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>87.37</t>
+          <t>19.58999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.6225</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4659,27 +4659,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
+          <t>0x8f4d5275f1795012e3dc501b6d97126a38f8d1c8d8575402bd2170dd78519821</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4704,17 +4704,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785602986</t>
+          <t>1785607696</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>188.398922</t>
+          <t>31.469863</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
+          <t>0x4b775276103651c2ad53157299d4707b268432c1cb7e4bd3353b54635947b9c4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4739,31 +4739,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.195</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AIK -2</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -4771,27 +4763,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
+          <t>0x2ef78d968212afb62887914e95aafbdae00c970ba8bf42d0c2a3151b547635de</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4816,17 +4808,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785599571</t>
+          <t>1785606822</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>20.161435</t>
+          <t>29.538462</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4843,28 +4835,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
+          <t>0x3037fa39457240cddcf8f8ee6f8e1e17b8531a603a7d6eb4a92ac18edccccb9c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4875,27 +4867,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4920,17 +4912,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604388</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>4.695652</t>
+          <t>7.782101</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4947,67 +4939,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
+          <t>0xde8207e16085f2b6f35e7dcda3ac161fe645050cd677beec42cdbba421805089</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>86.03757</t>
+          <t>11.21556</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5032,17 +5016,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785598914</t>
+          <t>1785604383</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>105.567571</t>
+          <t>17.524313</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5059,7 +5043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
+          <t>0x5a8f11b1cc3c9b675dd3330f3c58ef9fddc8df3b717beef386b840600e229f86</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5070,17 +5054,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5091,27 +5075,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>IF Brommapojkarna vs Malmo FF</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>IF Brommapojkarna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0xcf80ee4ba8f893428de4e8753f5d6819b917616ad7cc4e6580a255dd6984aad0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19611635</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5136,7 +5120,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785596049</t>
+          <t>1785604382</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5130,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>69.147541</t>
+          <t>17.78125</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,28 +5147,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
+          <t>0x7a6671baa8de892343f866dbe124d72350b61552ba61be0af42f35261787697c</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>28.17906</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.7075</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5210,7 +5194,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5240,7 +5224,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785595989</t>
+          <t>1785603319</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5250,7 +5234,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>39.82906</t>
+          <t>15.505376</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5267,28 +5251,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
+          <t>0x2c654920db2405320e0774ec0d4dfe32ec8db5d36fa9f9b01bdeab237f707389</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>87.37</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5314,7 +5298,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
+          <t>0xe141f32855b53f0b7a7b8323674f90753ba80a9381b746131c44fc54212cb2ef</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5344,7 +5328,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785595485</t>
+          <t>1785602986</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5354,7 +5338,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>188.398922</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5371,31 +5355,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
+          <t>0x1f740ac045a587cc9923c2ebf0cf53f4e36beee2790a2d7bae35d2a9a9fffd22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>AIK -2</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5403,27 +5395,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x2ccdb0a3731c2f8ac167545d5b1b6632ba855e51e8470104b9adfba823dc170e</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5448,17 +5440,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785577482</t>
+          <t>1785599571</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>20.161435</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5475,39 +5467,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
+          <t>0xf21a20b2a90620b166160ee239ca72e1f6ae5a932c692f9e142a197282be49aa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.345</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5515,27 +5499,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5560,17 +5544,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785577478</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>220.567976</t>
+          <t>4.695652</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5587,31 +5571,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
+          <t>0xcb49cf82547bf7e2dd3619708564ac9620d6faa3d096e2d2baef2e32ab2d5da1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>25.31488</t>
+          <t>86.03757</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4625</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5619,27 +5611,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x65f84989edb2d9bb7fdb44a48b0e88e3d8e46faeacceb526be691d06da275bd2</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5664,17 +5656,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785577466</t>
+          <t>1785598914</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>54.734876</t>
+          <t>105.567571</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5691,7 +5683,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
+          <t>0xe2c7a16a706e04dbdb9b4466345ac937b046d070e2ed4c3704f8741054b98146</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5699,19 +5691,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4112</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5719,11 +5707,7 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5731,27 +5715,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5776,17 +5760,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785596049</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>32.43769</t>
+          <t>69.147541</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,7 +5787,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
+          <t>0x05bb1bf6324de6c7cc64ee20aa3e8ef8c767a8d22377f031eb1a639200e59414</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5811,19 +5795,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.68997</t>
+          <t>28.17906</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3175</t>
+          <t>1.7075</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5831,11 +5811,7 @@
           <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -5843,27 +5819,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xc672163e8e266674113db270fe75fd2c599b1cd1d2e00348e61e90bf1bb59ab5</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5888,17 +5864,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785577433</t>
+          <t>1785595989</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>27.369984</t>
+          <t>39.82906</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5915,28 +5891,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
+          <t>0xc2a953cc41ab7f801d83b577ad7f10832256bc573af153541b2e358f5cc414bd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5947,27 +5923,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0x0183018083cb33d7b074f254bebaa3413708442aae08c6cc57dda5a78d18a968</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5992,17 +5968,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785577154</t>
+          <t>1785595485</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>10.781671</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6019,7 +5995,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
+          <t>0x9d4ba917a4233070f691ed2d65e5fd45d17fc2a9aa4b86b1e7754285709f1a50</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6027,11 +6003,7 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>5</t>
@@ -6039,7 +6011,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6047,34 +6019,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6104,7 +6072,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785577152</t>
+          <t>1785577482</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6114,7 +6082,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6131,31 +6099,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
+          <t>0x25175437c1864293aff6da819290c4f23f6e5d8c3fb218a5d2c1df6eeadb7921</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2.59603</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.4138</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6178,7 +6154,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6208,7 +6184,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785577149</t>
+          <t>1785577478</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6218,7 +6194,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>5.597908</t>
+          <t>220.567976</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6235,7 +6211,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
+          <t>0x87e11cf5e2a8ca3968841bf9209dd796714117c868380bdce172b827863d2861</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6243,19 +6219,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>25.31488</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.4625</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6263,34 +6235,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6320,7 +6288,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577466</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6330,7 +6298,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>70.347826</t>
+          <t>54.734876</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6347,12 +6315,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
+          <t>0xf111cf5e883a4401e26bee488f56f34ee6b47899f3932f607ab641db752498b8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6362,47 +6330,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>13.34</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.2288</t>
+          <t>1.4112</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6432,7 +6400,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6442,7 +6410,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>131.060109</t>
+          <t>32.43769</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6459,31 +6427,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
+          <t>0x63c18742e3c95b035683bda25c68d926aeb88056eec83deb28c25f4de485b108</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>50.98871</t>
+          <t>8.68997</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4638</t>
+          <t>1.3175</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6506,7 +6482,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6536,7 +6512,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577433</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6546,7 +6522,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>109.948701</t>
+          <t>27.369984</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6563,23 +6539,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
+          <t>0x9c01f452c50c348cc34b8dca9755c3748e3f9d0e6cca96250d0ff421aab9959c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>68.58259</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6640,7 +6616,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785577133</t>
+          <t>1785577154</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6650,7 +6626,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>149.092587</t>
+          <t>10.781671</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6667,7 +6643,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
+          <t>0x91368452b5678367a61a7917a1a569ccd1a3dc1f82aa9bd471e16e1ff05d9867</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6675,7 +6651,11 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>5</t>
@@ -6683,7 +6663,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6691,7 +6671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6714,7 +6698,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6744,7 +6728,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785577004</t>
+          <t>1785577152</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6754,7 +6738,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>10.869565</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6771,23 +6755,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
+          <t>0xfd0275eabe21f8f8026ab87bc545a9ee8fe4f660dc5caa17bdba7222b466f67d</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.59603</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6848,7 +6832,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785576974</t>
+          <t>1785577149</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6858,7 +6842,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>21.73913</t>
+          <t>5.597908</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6875,7 +6859,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
+          <t>0x932f2bfb56c9bee82f1b9d1a9945a0b9f9a7f898a3f096de7adfeadbe8c40e31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6883,15 +6867,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>56.57148</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6899,7 +6887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -6922,7 +6914,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6952,7 +6944,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785576966</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6962,7 +6954,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>122.981478</t>
+          <t>70.347826</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6979,12 +6971,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
+          <t>0x34411a5839f5be9a91903f7842719d68a42a23ded65adc2cf2775813937a3fae</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6994,22 +6986,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>29.98</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.2288</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7034,7 +7026,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7064,7 +7056,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785576397</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7074,7 +7066,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>3.914373</t>
+          <t>131.060109</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7091,39 +7083,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
+          <t>0x20f06d87f1b22028325694f02391e7eee7515a91c4ab4b2ce1486f8810b1d714</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>50.98871</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4638</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7146,7 +7130,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7176,7 +7160,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7186,7 +7170,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>9.247706</t>
+          <t>109.948701</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7203,23 +7187,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
+          <t>0x077079735b1ec184534936016537f37cfa3b8e9590ed90584ee01988809e4b9c</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>65.05999</t>
+          <t>68.58259</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7250,7 +7234,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7280,7 +7264,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785575922</t>
+          <t>1785577133</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7290,7 +7274,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>84.220052</t>
+          <t>149.092587</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7307,39 +7291,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
+          <t>0xaf2c1d07a4d405b3aae0a943a8242f47ff379594ca8de77f36bbd3c63dae7a6b</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7362,7 +7338,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7392,7 +7368,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785575403</t>
+          <t>1785577004</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7402,7 +7378,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>223.686275</t>
+          <t>10.869565</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7419,7 +7395,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
+          <t>0x485725aa6579c21b80ccd3593c09203347ec9a39a135dd363d8f240b1b4d10c9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7427,31 +7403,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3188</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -7474,7 +7442,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7504,7 +7472,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785575290</t>
+          <t>1785576974</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7514,7 +7482,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>6.682353</t>
+          <t>21.73913</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7531,23 +7499,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
+          <t>0x8ee173a53d6d07562ff5199bffede08b309a95be1c05f88fb444d940adcb91e1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10.45999</t>
+          <t>56.57148</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7725</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7578,7 +7546,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7608,7 +7576,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785575084</t>
+          <t>1785576966</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7618,7 +7586,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>13.54044</t>
+          <t>122.981478</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7635,12 +7603,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
+          <t>0x6f86b027c5636060745f80e9dd1912c9928cd11a23192a6ee5654b67a4218bd7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7650,39 +7618,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5463</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7690,7 +7658,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7720,7 +7688,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785574733</t>
+          <t>1785576397</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7730,7 +7698,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>9.1533</t>
+          <t>3.914373</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7747,12 +7715,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
+          <t>0x7140abffa94779f2bba35d7f04eb1fd97e2e42410f76e514f40d951ac065d0f6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7762,39 +7730,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.59139</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -7802,7 +7770,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7832,7 +7800,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7842,7 +7810,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>4.733132</t>
+          <t>9.247706</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7859,7 +7827,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
+          <t>0x6761c30948dc23f0a62ff5b9dc29644c93c319e7f80dd993f941b472d15ac365</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7870,12 +7838,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>65.05999</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7906,7 +7874,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7936,7 +7904,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785574712</t>
+          <t>1785575922</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7946,7 +7914,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36.043478</t>
+          <t>84.220052</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7963,12 +7931,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
+          <t>0x8c96b85ae303ae03bc13b9b1bb9d96da988b9683fdad8ca24b67321e8f2e7296</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7978,39 +7946,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8018,7 +7986,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8048,7 +8016,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785574711</t>
+          <t>1785575403</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8058,7 +8026,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>41.953917</t>
+          <t>223.686275</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8075,12 +8043,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
+          <t>0x1f62d0cd835774bff1119f052cfe1cccf188deca7f155a342f310bb998197725</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8090,39 +8058,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>65.38999</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5387</t>
+          <t>1.3188</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>Bk Hacken -1.5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8130,7 +8098,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8160,7 +8128,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785574671</t>
+          <t>1785575290</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8170,7 +8138,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>121.373531</t>
+          <t>6.682353</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8187,7 +8155,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
+          <t>0x2b108f3798a0efeece0bd985c661b40acbcfe24a8ec2fe351d6586c8644e40bf</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8195,19 +8163,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>10.45999</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.7725</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8215,11 +8179,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8272,7 +8232,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785574668</t>
+          <t>1785575084</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8282,7 +8242,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>78.340426</t>
+          <t>13.54044</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8299,36 +8259,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
+          <t>0x656c98402f8fd3db8065c95386e5a04f55eee0a3e69482c0a2be22b342533e0f</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>110.32</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.5463</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -8346,7 +8314,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8376,7 +8344,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574733</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8386,7 +8354,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>370.823529</t>
+          <t>9.1533</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8403,12 +8371,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
+          <t>0x59bcedbea16a3719a3f278e7deb543c2fd0854a9d49f3ef366e069ec2cde61e0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8418,12 +8386,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1e-05</t>
+          <t>2.59139</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8433,7 +8401,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8458,7 +8426,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8488,7 +8456,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785574667</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8498,7 +8466,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>0.000043</t>
+          <t>4.733132</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8515,28 +8483,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
+          <t>0x1b14046f92de38f3246ce9ecb2a522e42860f6f369568ab5403951f9c4e8cc02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>39.62258</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8562,7 +8530,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8592,7 +8560,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574712</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8602,7 +8570,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>66.592571</t>
+          <t>36.043478</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8619,31 +8587,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
+          <t>0xa76333d2192f0e00bd5f09fffa128f800781c2dfabe5a195120c7676017d5267</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>23.09033</t>
+          <t>22.76</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.4612</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -8666,7 +8642,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8696,7 +8672,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574711</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8706,7 +8682,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>50.060336</t>
+          <t>41.953917</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8723,7 +8699,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
+          <t>0x342934693d5989fd0fbd5d44b1d23578f4b04f764f97b6a1e9683308377b960f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8731,28 +8707,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8.39352</t>
+          <t>65.38999</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.2975</t>
+          <t>1.5387</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>Allsvenskan</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>Bk Hacken vs Kalmar FF</t>
@@ -8770,7 +8754,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8800,7 +8784,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574671</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8810,7 +8794,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>28.213513</t>
+          <t>121.373531</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8827,12 +8811,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
+          <t>0x447993787cc8b7f043bdfead21c642902dcc8eb8da114889bc22a849b1c87405</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8842,12 +8826,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>22.83872</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8857,24 +8841,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -8882,7 +8866,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8912,7 +8896,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785574666</t>
+          <t>1785574668</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8922,7 +8906,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>42.002244</t>
+          <t>78.340426</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8939,28 +8923,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
+          <t>0x49e5897dde1e991b633ff3f4721e72cf01a55eb3ef0d840c7751b1a2fd186cf5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>99.66667</t>
+          <t>110.32</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Allsvenskan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8986,7 +8970,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xf8ab17b6391d719de48ff9e51d1fda95601b8cd6f72f5d73e945dae350fa7620</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9016,7 +9000,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785574665</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9026,7 +9010,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>216.666674</t>
+          <t>370.823529</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9043,7 +9027,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
+          <t>0x2b5bcd1fa03055ff4fb9c98dbf8c24d700511031f0dad6ff3930fa8c4c32aed0</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9058,12 +9042,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>1e-05</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9128,7 +9112,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785572695</t>
+          <t>1785574667</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9138,7 +9122,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>42.508108</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9155,28 +9139,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
+          <t>0x94c77eab3b755c1a38f47c730fd26f085e7455126ba2f874bc2006f38c266770</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>60.49999</t>
+          <t>39.62258</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.7775</t>
+          <t>1.595</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9202,7 +9186,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9232,7 +9216,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785569861</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9242,7 +9226,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>77.813492</t>
+          <t>66.592571</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9259,39 +9243,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
+          <t>0x23695b8e4a42f02f4d66505abc6956f47947fa66d0f778f5886e7494e60d3ecc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20.57</t>
+          <t>23.09033</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.4612</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9314,7 +9290,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
+          <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9344,7 +9320,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785568816</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9354,7 +9330,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>50.060336</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9371,39 +9347,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
+          <t>0x1f7350f0b60c853371194bac68a9efda96c64efc4890b15e35038bdf60ccb803</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8.39352</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.2975</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9411,27 +9379,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x6155db39ffa02b35e713474b081feaa6b9dac9d54f16e186b21a1b376909b997</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9456,17 +9424,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785567910</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>16.064257</t>
+          <t>28.213513</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9483,12 +9451,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
+          <t>0x0ec7de8c2faa05e33c5bddca9278541a4cbaa6276fe7ff136563c3de78a22558</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9498,22 +9466,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>15.85</t>
+          <t>22.83872</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3113</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9523,27 +9491,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Djurgardens IF vs VasterAs SK FK</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>VasterAs SK FK</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19619060</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9568,17 +9536,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785567898</t>
+          <t>1785574666</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1785776400</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>50.923695</t>
+          <t>42.002244</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9595,27 +9563,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
+          <t>0x0168b274568d6a5bb0460a6b698d38f61daeedaf6162a6ffe06e0640731a8e01</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>99.66667</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.2263</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9623,34 +9587,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Kalmar FF</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9680,7 +9640,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785566254</t>
+          <t>1785574665</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9690,7 +9650,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>75.138122</t>
+          <t>216.666674</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9707,12 +9667,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
+          <t>0x8f6263643eaf5bab73400ed9f8ba58d4dfe1caa1604b899f1ba8584fba16427d</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9722,12 +9682,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10.89998</t>
+          <t>9.83</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -9737,24 +9697,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -9762,7 +9722,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9792,7 +9752,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785565064</t>
+          <t>1785572695</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9802,7 +9762,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>19.639604</t>
+          <t>42.508108</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9819,27 +9779,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
+          <t>0xe72e59737fd7e555f96742f779d7a3480396e8b5a54ecc67ebb69c2010917401</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.99999</t>
+          <t>60.49999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.6713</t>
+          <t>1.7775</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -9847,11 +9803,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>AIK</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9859,27 +9811,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AIK vs Orgryte IS</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Orgryte IS</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19612553</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9904,17 +9856,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785564110</t>
+          <t>1785569861</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785681000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1.489743</t>
+          <t>77.813492</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9931,23 +9883,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
+          <t>0x1fe6d1a73852eff74a18abad9fd5206a2f4a24e95968644acc5573f65474c7f3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>65.90999</t>
+          <t>20.57</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9955,7 +9911,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -9978,7 +9938,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0xa663dda3daef8029bdca19eb0136d844cfe79c076e020eec59ab5de83985de08</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10008,7 +9968,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785562879</t>
+          <t>1785568816</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10018,7 +9978,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>84.095681</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10035,31 +9995,39 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
+          <t>0xc99416ee569d3c8ba6dc8aeb879866d9f0f17dafe460132d5b701e44d0cf6bae</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>11.20999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10067,27 +10035,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -10112,17 +10080,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785561095</t>
+          <t>1785567910</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>18.722322</t>
+          <t>16.064257</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10139,31 +10107,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
+          <t>0x0ffba54f02ffac26db0541a62b26edf49adb7a87fca9d95cd7d6c8fdeb1114ee</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>15.85</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.5987</t>
+          <t>1.3113</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10171,27 +10147,27 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>Djurgardens IF vs VasterAs SK FK</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>VasterAs SK FK</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xe9485ad8199ec14a4d262ecde0fe91091ad341ed75379c1045ccf88753634eb4</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19619060</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10216,17 +10192,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785567898</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785776400</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>45.878914</t>
+          <t>50.923695</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10243,31 +10219,39 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
+          <t>0xda32ce2ffa21bf6b4121d6487107f20f5a6abeb2caa408495a96996640dafc5c</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.2125</t>
+          <t>1.2263</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10290,7 +10274,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10320,7 +10304,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785554384</t>
+          <t>1785566254</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10330,7 +10314,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>11.105882</t>
+          <t>75.138122</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10347,23 +10331,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
+          <t>0xecde8f04a30e0b20b8a81b70c092a3d7450e9ae9d37df916bacbce31151c81f4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>0xcF597434D48cDA55032b9d4931a0FFAeeEe7fb0D</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2.45998</t>
+          <t>10.89998</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.7837</t>
+          <t>1.555</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10371,7 +10359,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10394,7 +10386,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10424,7 +10416,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1785551845</t>
+          <t>1785565064</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10434,7 +10426,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>3.13873</t>
+          <t>19.639604</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10451,12 +10443,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
+          <t>0xbb9b8bc19f2a98b243184fea2ec71fd64f273f77372cb8b882b71d95c21c7728</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xAB03DDB118c18F7EfC711f056a7A4B5D25e040aA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10466,22 +10458,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>18.16</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.4025</t>
+          <t>1.6713</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IFK Göteborg -1</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10491,27 +10483,27 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>AIK vs Orgryte IS</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Orgryte IS</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
+          <t>0x50b9cba310bde017a0c739b1ed3f6aa2beb007086eccef7e6a33aa42f38a30b2</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19612553</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -10536,17 +10528,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1785549936</t>
+          <t>1785564110</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785681000</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>45.118012</t>
+          <t>1.489743</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10563,27 +10555,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
+          <t>0x7c504ddf537756764dd43eb9a131b762c9ba8f8cc949d6645e72e10c83f21063</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>65.90999</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.5587</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10591,26 +10579,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>Bk Hacken</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allsvenskan</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Bk Hacken vs Kalmar FF</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Bk Hacken</t>
-        </is>
-      </c>
       <c r="K95" t="inlineStr">
         <is>
           <t>Kalmar FF</t>
@@ -10618,7 +10602,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10648,7 +10632,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1785542520</t>
+          <t>1785562879</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10658,7 +10642,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>135.803132</t>
+          <t>84.095681</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10675,7 +10659,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
+          <t>0x6f3e7743442fb682fb7456b2d46b9e282d6cf2805a09412bed1df58bcb0f25fa</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10683,31 +10667,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>9.76138</t>
+          <t>11.20999</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10730,7 +10706,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10760,7 +10736,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1785542512</t>
+          <t>1785561095</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10770,7 +10746,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>23.241381</t>
+          <t>18.722322</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10787,7 +10763,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
+          <t>0xf79cad88861fe97643d530a954105651d53233b3dc3400d28672cf0228734d75</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10795,31 +10771,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.325</t>
+          <t>1.5987</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Bk Hacken -1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -10842,7 +10810,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10872,7 +10840,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1785542511</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10882,7 +10850,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>9.353846</t>
+          <t>45.878914</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10899,7 +10867,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
+          <t>0x046f0ceab1be31910c8620a38862e49fd7750e24967b6bf9892858e993faf37b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10910,17 +10878,17 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.1687</t>
+          <t>1.2125</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -10946,7 +10914,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0x49fcc0f18d956d6482cf5667b5b1149bbe7026d2074e1e80409ee30387d46cec</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10976,7 +10944,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1785535711</t>
+          <t>1785554384</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10986,7 +10954,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>17.718519</t>
+          <t>11.105882</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11003,7 +10971,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
+          <t>0x28bdc681c197224e73a85a8d30cd57dd36f694e842ca6367666d3a68b38ac2ed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11014,17 +10982,17 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.45998</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.7837</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -11050,7 +11018,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+          <t>0xd54da505803bccb6eaf9636ccc57841cc524069f76b734af179b0e9e49cbb1a3</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11080,7 +11048,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785551845</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11090,7 +11058,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>11.941176</t>
+          <t>3.13873</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11107,7 +11075,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+          <t>0xb129063f1f0b30b4d7252a18ecc7328754497ce715db9f126efad5ca75a2b320</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11122,12 +11090,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.4025</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -11137,7 +11105,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>IFK Göteborg -1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -11147,27 +11115,27 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Bk Hacken vs Kalmar FF</t>
+          <t>IFK Göteborg vs Degerfors IF</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Bk Hacken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Degerfors IF</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0x6061e6a8201250047f36b93638a4e1d5999ad766534db1358c0fb4a884ad8b73</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>L19603365</t>
+          <t>L19611663</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -11192,17 +11160,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1785534359</t>
+          <t>1785549936</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>1785589200</t>
+          <t>1785672000</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>45.969789</t>
+          <t>45.118012</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11219,12 +11187,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+          <t>0x97fb68c6b0654285730a3a66c3c80b9103b30b1f112c9ac4836b9595a2ef4e71</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11234,22 +11202,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3.80999</t>
+          <t>75.88</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.5587</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11274,7 +11242,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+          <t>0x49f727dea2051712953b143baac8414bf3fc6b8e4af7b41e3bc6f790b7eb8c76</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11304,7 +11272,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1785533370</t>
+          <t>1785542520</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11314,7 +11282,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>6.047603</t>
+          <t>135.803132</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11331,7 +11299,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+          <t>0x9797afcb9d30c17dec634b6ff58745eeb94db1c4ac70d769a82e05e05885508b</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11346,22 +11314,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>9.76138</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Bk Hacken -1</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -11386,7 +11354,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11416,7 +11384,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1785531926</t>
+          <t>1785542512</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11426,7 +11394,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>13.555556</t>
+          <t>23.241381</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11443,12 +11411,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+          <t>0x632a3319e0390f2445b119d62cf014f870f67ac94f9a9be3fdc427f4eeb95d27</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11458,22 +11426,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.4138</t>
+          <t>1.325</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bk Hacken -1</t>
+          <t>Bk Hacken -1.5</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11498,7 +11466,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+          <t>0xe0d0ea5ed9a9531a0d9a8b407267f4c0893be1d9ba5c685289846562b7028cfd</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11528,7 +11496,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1785494939</t>
+          <t>1785542511</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11538,7 +11506,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>54.960725</t>
+          <t>9.353846</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11555,39 +11523,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+          <t>0x4b2dea0a5cd4780ebce17ec4dce7e5cf57b818b023f71fcfbd42c674725a80c4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Degerfors IF</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>Allsvenskan</t>
@@ -11595,27 +11555,27 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>IFK Göteborg vs Degerfors IF</t>
+          <t>Bk Hacken vs Kalmar FF</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bk Hacken</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Degerfors IF</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>L19611663</t>
+          <t>L19603365</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -11640,17 +11600,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1785438282</t>
+          <t>1785535711</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>1785672000</t>
+          <t>1785589200</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>100.069364</t>
+          <t>17.718519</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11667,28 +11627,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
+          <t>0xd43f11093fb4e01c177abb19edf80d9c2efd9bcd10c8449183d688e169b2bce8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.4675</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -11714,55 +11674,719 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
+          <t>0x60de0488d91de8628b08a39003f35a0066dbe671648bc58f6f89c95fb9cfb68e</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>11.941176</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0x35f6e6f55b350735989f9c70a551b1b492f303f60f6678083396f661c79ea471</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19.02</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1785534359</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>45.969789</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0xd766698e466705ae38c06d2671575880d72ce6bdf5578c2232a0bd68fe1fc381</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3.80999</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0x375d16e033e4bf094778b7ce9aeabd07dff76d4d30065384ea982ca4aa8eb631</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1785533370</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>6.047603</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0x5f64f46f8a4871fdf08e07293583bd28a4d596df6764cb46556941dd6d4b7b52</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.405</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0xfdddf3a17c3a7b3379814e0885a917a56bc0e70e3d5a5c0b6beddc6ba3dd7921</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1785531926</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>13.555556</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0x35bb1d2972a8c9e91d82c92876853d73d00586e7e2c90b244e71ce4f8e12960f</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>22.74</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.4138</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Bk Hacken -1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0xf0439368071f4ba1f42bafda2c7f19a05013f714bf1536ea251802b6df91ec1b</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>L19603365</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1785494939</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>1785589200</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>54.960725</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0xeddd06e40edd8856b30731382ee5fb74db2f3dbbbc54751058e572781b2ac653</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>21.64</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>IFK Göteborg vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>IFK Göteborg</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Degerfors IF</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0x95df1e46a343a30f473be7ab5a70c9f8e18084926552a6d0d301a05441a92e59</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>L19611663</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1785438282</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>1785672000</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>100.069364</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0xde6503f90cec6a47ec5bc8d0a6eea4689c53194f97fad2aebac3314c4e9bbf7b</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0x86aaA5Ea1D96e252c2C62869556dF1346F9a9264</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.4675</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Allsvenskan</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Bk Hacken vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Bk Hacken</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Kalmar FF</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
           <t>0xad3b2a98263dca104b4acedfd4bd63e633d2e4f24af4a64ff9bb28a9491fc8c3</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>L19603365</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
         <is>
           <t>1785411359</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>1785589200</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="T111" t="inlineStr">
         <is>
           <t>4.791444</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="U111" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr">
+      <c r="V111" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
